--- a/hall/resources/sample/GrowthFund.xlsx
+++ b/hall/resources/sample/GrowthFund.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF4BD31-3383-4474-95C9-7ED6796897B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12510" yWindow="4815" windowWidth="15330" windowHeight="10935" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GrowthFund" sheetId="1" r:id="rId1"/>
@@ -32,16 +26,51 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+仅配置1个道具</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>序列ID</t>
   </si>
   <si>
+    <t>类型 1免费 2付费</t>
+  </si>
+  <si>
     <t>达成条件(角色等级)</t>
   </si>
   <si>
-    <t>免费道具奖励</t>
+    <t>道具奖励</t>
   </si>
   <si>
     <t>int</t>
@@ -53,144 +82,140 @@
     <t>id</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>level</t>
   </si>
   <si>
+    <t>getItem</t>
+  </si>
+  <si>
     <t>1990000_10000</t>
   </si>
   <si>
+    <t>1990000_20000</t>
+  </si>
+  <si>
+    <t>1990000_30000</t>
+  </si>
+  <si>
+    <t>1990000_40000</t>
+  </si>
+  <si>
+    <t>1990000_50000</t>
+  </si>
+  <si>
+    <t>1990000_60000</t>
+  </si>
+  <si>
+    <t>1990000_70000</t>
+  </si>
+  <si>
+    <t>1990000_80000</t>
+  </si>
+  <si>
+    <t>1990000_90000</t>
+  </si>
+  <si>
     <t>1990000_100000</t>
   </si>
   <si>
-    <t>1990000_20000</t>
+    <t>1990000_110000</t>
+  </si>
+  <si>
+    <t>1990000_120000</t>
+  </si>
+  <si>
+    <t>1990000_130000</t>
+  </si>
+  <si>
+    <t>1990000_140000</t>
+  </si>
+  <si>
+    <t>1990000_150000</t>
+  </si>
+  <si>
+    <t>1990000_160000</t>
+  </si>
+  <si>
+    <t>1990000_170000</t>
+  </si>
+  <si>
+    <t>1990000_180000</t>
+  </si>
+  <si>
+    <t>1990000_190000</t>
   </si>
   <si>
     <t>1990000_200000</t>
   </si>
   <si>
-    <t>1990000_30000</t>
-  </si>
-  <si>
     <t>1990000_300000</t>
   </si>
   <si>
-    <t>1990000_40000</t>
-  </si>
-  <si>
     <t>1990000_400000</t>
   </si>
   <si>
-    <t>1990000_50000</t>
-  </si>
-  <si>
     <t>1990000_500000</t>
   </si>
   <si>
-    <t>1990000_60000</t>
-  </si>
-  <si>
     <t>1990000_600000</t>
   </si>
   <si>
-    <t>1990000_70000</t>
-  </si>
-  <si>
     <t>1990000_700000</t>
   </si>
   <si>
-    <t>1990000_80000</t>
-  </si>
-  <si>
     <t>1990000_800000</t>
   </si>
   <si>
-    <t>1990000_90000</t>
-  </si>
-  <si>
     <t>1990000_900000</t>
   </si>
   <si>
     <t>1990000_1000000</t>
   </si>
   <si>
-    <t>1990000_110000</t>
-  </si>
-  <si>
     <t>1990000_1100000</t>
   </si>
   <si>
-    <t>1990000_120000</t>
-  </si>
-  <si>
     <t>1990000_1200000</t>
   </si>
   <si>
-    <t>1990000_130000</t>
-  </si>
-  <si>
     <t>1990000_1300000</t>
   </si>
   <si>
-    <t>1990000_140000</t>
-  </si>
-  <si>
     <t>1990000_1400000</t>
   </si>
   <si>
-    <t>1990000_150000</t>
-  </si>
-  <si>
     <t>1990000_1500000</t>
   </si>
   <si>
-    <t>1990000_160000</t>
-  </si>
-  <si>
     <t>1990000_1600000</t>
   </si>
   <si>
-    <t>1990000_170000</t>
-  </si>
-  <si>
     <t>1990000_1700000</t>
   </si>
   <si>
-    <t>1990000_180000</t>
-  </si>
-  <si>
     <t>1990000_1800000</t>
   </si>
   <si>
-    <t>1990000_190000</t>
-  </si>
-  <si>
     <t>1990000_1900000</t>
   </si>
   <si>
     <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>getItem</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型 1免费 2付费</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,27 +241,168 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,12 +411,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -258,17 +604,259 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -277,27 +865,68 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -575,73 +1204,73 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.875" style="2" customWidth="1"/>
     <col min="5" max="6" width="9.25" style="2"/>
     <col min="7" max="7" width="9.25" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>48</v>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>46</v>
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" s="1" customFormat="1" spans="1:4">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -652,59 +1281,61 @@
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="2">
         <v>2</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="2">
         <v>4</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -715,62 +1346,64 @@
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="2">
         <v>6</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>60</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="1">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
         <v>70</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="2">
         <v>8</v>
       </c>
       <c r="B12" s="2">
         <v>1</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>80</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -781,489 +1414,511 @@
         <v>90</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="2">
         <v>10</v>
       </c>
       <c r="B14" s="2">
         <v>1</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>100</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="1">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
         <v>105</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="2">
         <v>12</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>110</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="1">
-        <v>1</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
         <v>115</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="2">
         <v>14</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>120</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="1">
-        <v>1</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="B19" s="2">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1">
         <v>125</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="2">
         <v>16</v>
       </c>
       <c r="B20" s="2">
         <v>1</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <v>130</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="1">
-        <v>1</v>
-      </c>
-      <c r="C21" s="2">
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
         <v>135</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="2">
         <v>18</v>
       </c>
       <c r="B22" s="2">
         <v>1</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>140</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="1">
-        <v>1</v>
-      </c>
-      <c r="C23" s="2">
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1">
         <v>145</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="2">
         <v>20</v>
       </c>
       <c r="B24" s="2">
         <v>1</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <v>150</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>21</v>
-      </c>
-      <c r="B25" s="2">
-        <v>2</v>
-      </c>
-      <c r="C25" s="1">
+    <row r="25" spans="1:6">
+      <c r="A25" s="5">
+        <v>101</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2</v>
+      </c>
+      <c r="C25" s="5">
         <v>10</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>8</v>
+      <c r="D25" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>22</v>
-      </c>
-      <c r="B26" s="2">
-        <v>2</v>
-      </c>
-      <c r="C26" s="2">
+    <row r="26" spans="1:6">
+      <c r="A26" s="5">
+        <v>102</v>
+      </c>
+      <c r="B26" s="5">
+        <v>2</v>
+      </c>
+      <c r="C26" s="5">
         <v>20</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="D26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>23</v>
-      </c>
-      <c r="B27" s="2">
-        <v>2</v>
-      </c>
-      <c r="C27" s="2">
+    <row r="27" spans="1:6">
+      <c r="A27" s="5">
+        <v>103</v>
+      </c>
+      <c r="B27" s="5">
+        <v>2</v>
+      </c>
+      <c r="C27" s="5">
         <v>30</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>12</v>
+      <c r="D27" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>24</v>
-      </c>
-      <c r="B28" s="2">
-        <v>2</v>
-      </c>
-      <c r="C28" s="2">
+    <row r="28" spans="1:6">
+      <c r="A28" s="5">
+        <v>104</v>
+      </c>
+      <c r="B28" s="5">
+        <v>2</v>
+      </c>
+      <c r="C28" s="5">
         <v>40</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="D28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2">
-        <v>2</v>
-      </c>
-      <c r="C29" s="1">
+    <row r="29" spans="1:6">
+      <c r="A29" s="5">
+        <v>105</v>
+      </c>
+      <c r="B29" s="5">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5">
         <v>50</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>16</v>
+      <c r="D29" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>26</v>
-      </c>
-      <c r="B30" s="2">
-        <v>2</v>
-      </c>
-      <c r="C30" s="2">
+    <row r="30" spans="1:6">
+      <c r="A30" s="5">
+        <v>106</v>
+      </c>
+      <c r="B30" s="5">
+        <v>2</v>
+      </c>
+      <c r="C30" s="5">
         <v>60</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="D30" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>27</v>
-      </c>
-      <c r="B31" s="2">
-        <v>2</v>
-      </c>
-      <c r="C31" s="2">
+    <row r="31" spans="1:6">
+      <c r="A31" s="5">
+        <v>107</v>
+      </c>
+      <c r="B31" s="5">
+        <v>2</v>
+      </c>
+      <c r="C31" s="5">
         <v>70</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>20</v>
+      <c r="D31" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>28</v>
-      </c>
-      <c r="B32" s="2">
-        <v>2</v>
-      </c>
-      <c r="C32" s="2">
+    <row r="32" spans="1:6">
+      <c r="A32" s="5">
+        <v>108</v>
+      </c>
+      <c r="B32" s="5">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
         <v>80</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="D32" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="1"/>
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="1">
-        <v>29</v>
-      </c>
-      <c r="B33" s="2">
-        <v>2</v>
-      </c>
-      <c r="C33" s="1">
+    <row r="33" spans="1:6">
+      <c r="A33" s="5">
+        <v>109</v>
+      </c>
+      <c r="B33" s="5">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
         <v>90</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>24</v>
+      <c r="D33" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
-        <v>30</v>
-      </c>
-      <c r="B34" s="2">
-        <v>2</v>
-      </c>
-      <c r="C34" s="2">
+    <row r="34" spans="1:5">
+      <c r="A34" s="5">
+        <v>110</v>
+      </c>
+      <c r="B34" s="5">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
         <v>100</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
-        <v>31</v>
-      </c>
-      <c r="B35" s="2">
-        <v>2</v>
-      </c>
-      <c r="C35" s="2">
+      <c r="D34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5">
+        <v>111</v>
+      </c>
+      <c r="B35" s="5">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
         <v>105</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
-        <v>32</v>
-      </c>
-      <c r="B36" s="2">
-        <v>2</v>
-      </c>
-      <c r="C36" s="2">
+      <c r="D35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5">
+        <v>112</v>
+      </c>
+      <c r="B36" s="5">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
         <v>110</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
-        <v>33</v>
-      </c>
-      <c r="B37" s="2">
-        <v>2</v>
-      </c>
-      <c r="C37" s="2">
+      <c r="D36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5">
+        <v>113</v>
+      </c>
+      <c r="B37" s="5">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
         <v>115</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="2">
-        <v>34</v>
-      </c>
-      <c r="B38" s="2">
-        <v>2</v>
-      </c>
-      <c r="C38" s="2">
+      <c r="D37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5">
+        <v>114</v>
+      </c>
+      <c r="B38" s="5">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
         <v>120</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="2">
-        <v>35</v>
-      </c>
-      <c r="B39" s="2">
-        <v>2</v>
-      </c>
-      <c r="C39" s="2">
+      <c r="D38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5">
+        <v>115</v>
+      </c>
+      <c r="B39" s="5">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
         <v>125</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
-        <v>36</v>
-      </c>
-      <c r="B40" s="2">
-        <v>2</v>
-      </c>
-      <c r="C40" s="2">
+      <c r="D39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5">
+        <v>116</v>
+      </c>
+      <c r="B40" s="5">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
         <v>130</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="2">
-        <v>37</v>
-      </c>
-      <c r="B41" s="2">
-        <v>2</v>
-      </c>
-      <c r="C41" s="2">
+      <c r="D40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5">
+        <v>117</v>
+      </c>
+      <c r="B41" s="5">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
         <v>135</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
-        <v>38</v>
-      </c>
-      <c r="B42" s="2">
-        <v>2</v>
-      </c>
-      <c r="C42" s="2">
+      <c r="D41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5">
+        <v>118</v>
+      </c>
+      <c r="B42" s="5">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
         <v>140</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="2">
-        <v>39</v>
-      </c>
-      <c r="B43" s="2">
-        <v>2</v>
-      </c>
-      <c r="C43" s="2">
+      <c r="D42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5">
+        <v>119</v>
+      </c>
+      <c r="B43" s="5">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
         <v>145</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="1">
-        <v>40</v>
-      </c>
-      <c r="B44" s="2">
-        <v>2</v>
-      </c>
-      <c r="C44" s="2">
+      <c r="D43" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5">
+        <v>120</v>
+      </c>
+      <c r="B44" s="5">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
         <v>150</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="D44" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/GrowthFund.xlsx
+++ b/hall/resources/sample/GrowthFund.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
   <si>
     <t>序列ID</t>
   </si>
@@ -151,6 +151,9 @@
     <t>1990000_200000</t>
   </si>
   <si>
+    <t>1990000_210000</t>
+  </si>
+  <si>
     <t>1990000_300000</t>
   </si>
   <si>
@@ -203,6 +206,9 @@
   </si>
   <si>
     <t>1990000_2000000</t>
+  </si>
+  <si>
+    <t>1990000_2200000</t>
   </si>
 </sst>
 </file>
@@ -391,12 +397,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1210,7 +1216,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
@@ -1278,7 +1284,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -1292,7 +1298,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
@@ -1309,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>12</v>
@@ -1326,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>13</v>
@@ -1343,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>14</v>
@@ -1360,7 +1366,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>15</v>
@@ -1377,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>16</v>
@@ -1394,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
@@ -1411,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>18</v>
@@ -1428,7 +1434,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>19</v>
@@ -1445,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>20</v>
@@ -1479,7 +1485,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="1">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>22</v>
@@ -1496,7 +1502,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="1">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>23</v>
@@ -1513,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="1">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>24</v>
@@ -1530,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="1">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>25</v>
@@ -1547,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="1">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>26</v>
@@ -1564,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>27</v>
@@ -1581,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="1">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>28</v>
@@ -1598,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="1">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>29</v>
@@ -1607,63 +1613,64 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="5">
-        <v>101</v>
-      </c>
-      <c r="B25" s="5">
-        <v>2</v>
-      </c>
-      <c r="C25" s="5">
-        <v>10</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>19</v>
+    <row r="25" spans="1:7">
+      <c r="A25" s="1">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1">
+        <v>200</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="5">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>2</v>
       </c>
       <c r="C26" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="5">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B27" s="5">
         <v>2</v>
       </c>
       <c r="C27" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="5">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>2</v>
       </c>
       <c r="C28" s="5">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>31</v>
@@ -1673,13 +1680,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="5">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" s="5">
         <v>2</v>
       </c>
       <c r="C29" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>32</v>
@@ -1689,13 +1696,13 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="5">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B30" s="5">
         <v>2</v>
       </c>
       <c r="C30" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>33</v>
@@ -1705,13 +1712,13 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="5">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B31" s="5">
         <v>2</v>
       </c>
       <c r="C31" s="5">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>34</v>
@@ -1721,13 +1728,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="5">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B32" s="5">
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>35</v>
@@ -1737,13 +1744,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="5">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B33" s="5">
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>36</v>
@@ -1751,30 +1758,31 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:6">
       <c r="A34" s="5">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B34" s="5">
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B35" s="5">
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>38</v>
@@ -1783,13 +1791,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B36" s="5">
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>39</v>
@@ -1798,13 +1806,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B37" s="5">
         <v>2</v>
       </c>
       <c r="C37" s="5">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>40</v>
@@ -1813,7 +1821,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B38" s="5">
         <v>2</v>
@@ -1828,13 +1836,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B39" s="5">
         <v>2</v>
       </c>
       <c r="C39" s="5">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>42</v>
@@ -1843,13 +1851,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" s="5">
         <v>2</v>
       </c>
       <c r="C40" s="5">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>43</v>
@@ -1858,13 +1866,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B41" s="5">
         <v>2</v>
       </c>
       <c r="C41" s="5">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>44</v>
@@ -1873,13 +1881,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B42" s="5">
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>45</v>
@@ -1888,13 +1896,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B43" s="5">
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>46</v>
@@ -1903,18 +1911,47 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B44" s="5">
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>47</v>
       </c>
       <c r="E44" s="1"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5">
+        <v>120</v>
+      </c>
+      <c r="B45" s="5">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>190</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="5">
+        <v>121</v>
+      </c>
+      <c r="B46" s="5">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>200</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/GrowthFund.xlsx
+++ b/hall/resources/sample/GrowthFund.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
     <t>序列ID</t>
   </si>
@@ -91,124 +91,82 @@
     <t>getItem</t>
   </si>
   <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>1990000_30000</t>
-  </si>
-  <si>
-    <t>1990000_40000</t>
-  </si>
-  <si>
-    <t>1990000_50000</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
-  </si>
-  <si>
-    <t>1990000_70000</t>
-  </si>
-  <si>
-    <t>1990000_80000</t>
-  </si>
-  <si>
-    <t>1990000_90000</t>
-  </si>
-  <si>
-    <t>1990000_100000</t>
-  </si>
-  <si>
-    <t>1990000_110000</t>
-  </si>
-  <si>
-    <t>1990000_120000</t>
-  </si>
-  <si>
-    <t>1990000_130000</t>
+    <t>1990000_5000</t>
+  </si>
+  <si>
+    <t>1990000_16000</t>
+  </si>
+  <si>
+    <t>1990000_28000</t>
+  </si>
+  <si>
+    <t>1990000_39000</t>
+  </si>
+  <si>
+    <t>1990000_46000</t>
+  </si>
+  <si>
+    <t>1990000_64000</t>
+  </si>
+  <si>
+    <t>1990000_81000</t>
+  </si>
+  <si>
+    <t>1990000_102000</t>
+  </si>
+  <si>
+    <t>1990000_125000</t>
   </si>
   <si>
     <t>1990000_140000</t>
   </si>
   <si>
-    <t>1990000_150000</t>
-  </si>
-  <si>
-    <t>1990000_160000</t>
-  </si>
-  <si>
-    <t>1990000_170000</t>
-  </si>
-  <si>
-    <t>1990000_180000</t>
-  </si>
-  <si>
-    <t>1990000_190000</t>
-  </si>
-  <si>
-    <t>1990000_200000</t>
-  </si>
-  <si>
-    <t>1990000_210000</t>
-  </si>
-  <si>
-    <t>1990000_300000</t>
-  </si>
-  <si>
-    <t>1990000_400000</t>
-  </si>
-  <si>
-    <t>1990000_500000</t>
-  </si>
-  <si>
-    <t>1990000_600000</t>
-  </si>
-  <si>
-    <t>1990000_700000</t>
-  </si>
-  <si>
-    <t>1990000_800000</t>
-  </si>
-  <si>
-    <t>1990000_900000</t>
-  </si>
-  <si>
-    <t>1990000_1000000</t>
-  </si>
-  <si>
-    <t>1990000_1100000</t>
-  </si>
-  <si>
-    <t>1990000_1200000</t>
-  </si>
-  <si>
-    <t>1990000_1300000</t>
-  </si>
-  <si>
-    <t>1990000_1400000</t>
-  </si>
-  <si>
-    <t>1990000_1500000</t>
-  </si>
-  <si>
-    <t>1990000_1600000</t>
-  </si>
-  <si>
-    <t>1990000_1700000</t>
-  </si>
-  <si>
-    <t>1990000_1800000</t>
-  </si>
-  <si>
-    <t>1990000_1900000</t>
-  </si>
-  <si>
-    <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>1990000_2200000</t>
+    <t>1990000_168000</t>
+  </si>
+  <si>
+    <t>1990000_171000</t>
+  </si>
+  <si>
+    <t>1990000_209000</t>
+  </si>
+  <si>
+    <t>1990000_43000</t>
+  </si>
+  <si>
+    <t>1990000_143000</t>
+  </si>
+  <si>
+    <t>1990000_243000</t>
+  </si>
+  <si>
+    <t>1990000_343000</t>
+  </si>
+  <si>
+    <t>1990000_405000</t>
+  </si>
+  <si>
+    <t>1990000_562000</t>
+  </si>
+  <si>
+    <t>1990000_719000</t>
+  </si>
+  <si>
+    <t>1990000_904000</t>
+  </si>
+  <si>
+    <t>1990000_1101000</t>
+  </si>
+  <si>
+    <t>1990000_1232000</t>
+  </si>
+  <si>
+    <t>1990000_1480000</t>
+  </si>
+  <si>
+    <t>1990000_1506000</t>
+  </si>
+  <si>
+    <t>1990000_1842000</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1174,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="2" customWidth="1"/>
@@ -1298,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
@@ -1315,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>12</v>
@@ -1332,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>13</v>
@@ -1349,10 +1307,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="1">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1366,10 +1324,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -1383,10 +1341,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1400,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -1417,10 +1375,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -1434,10 +1392,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="1">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -1451,10 +1409,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -1468,10 +1426,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="1">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1481,14 +1439,14 @@
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>1</v>
       </c>
       <c r="C17" s="1">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1502,10 +1460,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="1">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1519,10 +1477,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="1">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1536,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="1">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1549,14 +1507,14 @@
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>1</v>
       </c>
       <c r="C21" s="1">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1570,10 +1528,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="1">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1587,10 +1545,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="1">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1604,51 +1562,50 @@
         <v>1</v>
       </c>
       <c r="C24" s="1">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="1">
-        <v>21</v>
-      </c>
-      <c r="B25" s="2">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1">
-        <v>200</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>30</v>
+    <row r="25" spans="1:6">
+      <c r="A25" s="5">
+        <v>101</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2</v>
+      </c>
+      <c r="C25" s="5">
+        <v>5</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="5">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>2</v>
       </c>
       <c r="C26" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B27" s="5">
         <v>2</v>
@@ -1657,300 +1614,261 @@
         <v>15</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="5">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>2</v>
       </c>
       <c r="C28" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="5">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" s="5">
         <v>2</v>
       </c>
       <c r="C29" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="5">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B30" s="5">
         <v>2</v>
       </c>
       <c r="C30" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="5">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B31" s="5">
         <v>2</v>
       </c>
       <c r="C31" s="5">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="5">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B32" s="5">
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="5">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B33" s="5">
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:5">
       <c r="A34" s="5">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B34" s="5">
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B35" s="5">
         <v>2</v>
       </c>
       <c r="C35" s="5">
+        <v>55</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="5">
+        <v>112</v>
+      </c>
+      <c r="B36" s="5">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>60</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="5">
+        <v>113</v>
+      </c>
+      <c r="B37" s="5">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>65</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="5">
+        <v>114</v>
+      </c>
+      <c r="B38" s="5">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>70</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="5">
+        <v>115</v>
+      </c>
+      <c r="B39" s="5">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>75</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="5">
+        <v>116</v>
+      </c>
+      <c r="B40" s="5">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>80</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="5">
+        <v>117</v>
+      </c>
+      <c r="B41" s="5">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>85</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5">
+        <v>118</v>
+      </c>
+      <c r="B42" s="5">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
         <v>90</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5">
-        <v>111</v>
-      </c>
-      <c r="B36" s="5">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
+      <c r="D42" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="5">
+        <v>119</v>
+      </c>
+      <c r="B43" s="5">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>95</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="5">
+        <v>120</v>
+      </c>
+      <c r="B44" s="5">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
         <v>100</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5">
-        <v>112</v>
-      </c>
-      <c r="B37" s="5">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>110</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5">
-        <v>113</v>
-      </c>
-      <c r="B38" s="5">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>120</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5">
-        <v>114</v>
-      </c>
-      <c r="B39" s="5">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>130</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5">
-        <v>115</v>
-      </c>
-      <c r="B40" s="5">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>140</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E40" s="1"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5">
-        <v>116</v>
-      </c>
-      <c r="B41" s="5">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>150</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="1"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5">
-        <v>117</v>
-      </c>
-      <c r="B42" s="5">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>160</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E42" s="1"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5">
-        <v>118</v>
-      </c>
-      <c r="B43" s="5">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>170</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E43" s="1"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5">
-        <v>119</v>
-      </c>
-      <c r="B44" s="5">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>180</v>
-      </c>
       <c r="D44" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E44" s="1"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5">
-        <v>120</v>
-      </c>
-      <c r="B45" s="5">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>190</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E45" s="1"/>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="5">
-        <v>121</v>
-      </c>
-      <c r="B46" s="5">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>200</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GrowthFund.xlsx
+++ b/hall/resources/sample/GrowthFund.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>序列ID</t>
   </si>
@@ -91,82 +91,88 @@
     <t>getItem</t>
   </si>
   <si>
-    <t>1990000_5000</t>
-  </si>
-  <si>
-    <t>1990000_16000</t>
-  </si>
-  <si>
-    <t>1990000_28000</t>
+    <t>1990000_9000</t>
+  </si>
+  <si>
+    <t>1990000_19000</t>
+  </si>
+  <si>
+    <t>1990000_29000</t>
   </si>
   <si>
     <t>1990000_39000</t>
   </si>
   <si>
-    <t>1990000_46000</t>
-  </si>
-  <si>
-    <t>1990000_64000</t>
-  </si>
-  <si>
-    <t>1990000_81000</t>
-  </si>
-  <si>
-    <t>1990000_102000</t>
-  </si>
-  <si>
-    <t>1990000_125000</t>
-  </si>
-  <si>
-    <t>1990000_140000</t>
-  </si>
-  <si>
-    <t>1990000_168000</t>
-  </si>
-  <si>
-    <t>1990000_171000</t>
-  </si>
-  <si>
-    <t>1990000_209000</t>
-  </si>
-  <si>
-    <t>1990000_43000</t>
+    <t>1990000_42000</t>
+  </si>
+  <si>
+    <t>1990000_57000</t>
+  </si>
+  <si>
+    <t>1990000_73000</t>
+  </si>
+  <si>
+    <t>1990000_90000</t>
+  </si>
+  <si>
+    <t>1990000_109000</t>
+  </si>
+  <si>
+    <t>1990000_111000</t>
   </si>
   <si>
     <t>1990000_143000</t>
   </si>
   <si>
-    <t>1990000_243000</t>
-  </si>
-  <si>
-    <t>1990000_343000</t>
-  </si>
-  <si>
-    <t>1990000_405000</t>
-  </si>
-  <si>
-    <t>1990000_562000</t>
-  </si>
-  <si>
-    <t>1990000_719000</t>
-  </si>
-  <si>
-    <t>1990000_904000</t>
-  </si>
-  <si>
-    <t>1990000_1101000</t>
-  </si>
-  <si>
-    <t>1990000_1232000</t>
-  </si>
-  <si>
-    <t>1990000_1480000</t>
-  </si>
-  <si>
-    <t>1990000_1506000</t>
-  </si>
-  <si>
-    <t>1990000_1842000</t>
+    <t>1990000_176000</t>
+  </si>
+  <si>
+    <t>1990000_196000</t>
+  </si>
+  <si>
+    <t>1990000_242000</t>
+  </si>
+  <si>
+    <t>1990000_50000</t>
+  </si>
+  <si>
+    <t>1990000_99000</t>
+  </si>
+  <si>
+    <t>1990000_153000</t>
+  </si>
+  <si>
+    <t>1990000_207000</t>
+  </si>
+  <si>
+    <t>1990000_222000</t>
+  </si>
+  <si>
+    <t>1990000_304000</t>
+  </si>
+  <si>
+    <t>1990000_386000</t>
+  </si>
+  <si>
+    <t>1990000_475000</t>
+  </si>
+  <si>
+    <t>1990000_577000</t>
+  </si>
+  <si>
+    <t>1990000_585000</t>
+  </si>
+  <si>
+    <t>1990000_757000</t>
+  </si>
+  <si>
+    <t>1990000_930000</t>
+  </si>
+  <si>
+    <t>1990000_1036000</t>
+  </si>
+  <si>
+    <t>1990000_1281000</t>
   </si>
 </sst>
 </file>
@@ -355,12 +361,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1463,7 +1469,7 @@
         <v>70</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1480,7 +1486,7 @@
         <v>75</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1497,7 +1503,7 @@
         <v>80</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1514,7 +1520,7 @@
         <v>85</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1531,7 +1537,7 @@
         <v>90</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1548,7 +1554,7 @@
         <v>95</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1565,7 +1571,7 @@
         <v>100</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -1582,7 +1588,7 @@
         <v>5</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1598,7 +1604,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1614,7 +1620,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -1630,7 +1636,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -1646,7 +1652,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -1662,7 +1668,7 @@
         <v>30</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -1678,7 +1684,7 @@
         <v>35</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -1694,7 +1700,7 @@
         <v>40</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -1710,7 +1716,7 @@
         <v>45</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -1726,7 +1732,7 @@
         <v>50</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E34" s="1"/>
     </row>
@@ -1741,7 +1747,7 @@
         <v>55</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E35" s="1"/>
     </row>
@@ -1756,7 +1762,7 @@
         <v>60</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1770,7 +1776,7 @@
         <v>65</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1784,7 +1790,7 @@
         <v>70</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1798,7 +1804,7 @@
         <v>75</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1812,7 +1818,7 @@
         <v>80</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1826,7 +1832,7 @@
         <v>85</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1840,7 +1846,7 @@
         <v>90</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1854,7 +1860,7 @@
         <v>95</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1868,7 +1874,7 @@
         <v>100</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/GrowthFund.xlsx
+++ b/hall/resources/sample/GrowthFund.xlsx
@@ -91,88 +91,88 @@
     <t>getItem</t>
   </si>
   <si>
-    <t>1990000_9000</t>
-  </si>
-  <si>
-    <t>1990000_19000</t>
-  </si>
-  <si>
-    <t>1990000_29000</t>
-  </si>
-  <si>
-    <t>1990000_39000</t>
-  </si>
-  <si>
-    <t>1990000_42000</t>
-  </si>
-  <si>
-    <t>1990000_57000</t>
-  </si>
-  <si>
-    <t>1990000_73000</t>
-  </si>
-  <si>
-    <t>1990000_90000</t>
-  </si>
-  <si>
-    <t>1990000_109000</t>
-  </si>
-  <si>
-    <t>1990000_111000</t>
-  </si>
-  <si>
-    <t>1990000_143000</t>
-  </si>
-  <si>
-    <t>1990000_176000</t>
-  </si>
-  <si>
-    <t>1990000_196000</t>
-  </si>
-  <si>
-    <t>1990000_242000</t>
-  </si>
-  <si>
-    <t>1990000_50000</t>
-  </si>
-  <si>
-    <t>1990000_99000</t>
-  </si>
-  <si>
-    <t>1990000_153000</t>
-  </si>
-  <si>
-    <t>1990000_207000</t>
-  </si>
-  <si>
-    <t>1990000_222000</t>
-  </si>
-  <si>
-    <t>1990000_304000</t>
-  </si>
-  <si>
-    <t>1990000_386000</t>
-  </si>
-  <si>
-    <t>1990000_475000</t>
-  </si>
-  <si>
-    <t>1990000_577000</t>
-  </si>
-  <si>
-    <t>1990000_585000</t>
-  </si>
-  <si>
-    <t>1990000_757000</t>
-  </si>
-  <si>
-    <t>1990000_930000</t>
-  </si>
-  <si>
-    <t>1990000_1036000</t>
-  </si>
-  <si>
-    <t>1990000_1281000</t>
+    <t>1990000_66000</t>
+  </si>
+  <si>
+    <t>1990000_131000</t>
+  </si>
+  <si>
+    <t>1990000_202000</t>
+  </si>
+  <si>
+    <t>1990000_273000</t>
+  </si>
+  <si>
+    <t>1990000_294000</t>
+  </si>
+  <si>
+    <t>1990000_402000</t>
+  </si>
+  <si>
+    <t>1990000_510000</t>
+  </si>
+  <si>
+    <t>1990000_628000</t>
+  </si>
+  <si>
+    <t>1990000_764000</t>
+  </si>
+  <si>
+    <t>1990000_774000</t>
+  </si>
+  <si>
+    <t>1990000_1002000</t>
+  </si>
+  <si>
+    <t>1990000_1230000</t>
+  </si>
+  <si>
+    <t>1990000_1371000</t>
+  </si>
+  <si>
+    <t>1990000_1695000</t>
+  </si>
+  <si>
+    <t>1990000_350000</t>
+  </si>
+  <si>
+    <t>1990000_694000</t>
+  </si>
+  <si>
+    <t>1990000_1071000</t>
+  </si>
+  <si>
+    <t>1990000_1447000</t>
+  </si>
+  <si>
+    <t>1990000_1555000</t>
+  </si>
+  <si>
+    <t>1990000_2128000</t>
+  </si>
+  <si>
+    <t>1990000_2701000</t>
+  </si>
+  <si>
+    <t>1990000_3326000</t>
+  </si>
+  <si>
+    <t>1990000_4042000</t>
+  </si>
+  <si>
+    <t>1990000_4095000</t>
+  </si>
+  <si>
+    <t>1990000_5302000</t>
+  </si>
+  <si>
+    <t>1990000_6509000</t>
+  </si>
+  <si>
+    <t>1990000_7255000</t>
+  </si>
+  <si>
+    <t>1990000_8969000</t>
   </si>
 </sst>
 </file>
@@ -361,12 +361,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1192,7 +1192,7 @@
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1234,13 +1234,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:7">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:4">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1577,7 +1577,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>101</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" s="5">
         <v>102</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" s="5">
         <v>103</v>
       </c>
@@ -1625,7 +1625,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>104</v>
       </c>
@@ -1641,7 +1641,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" s="5">
         <v>105</v>
       </c>
@@ -1657,7 +1657,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30" s="5">
         <v>106</v>
       </c>
@@ -1673,7 +1673,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31" s="5">
         <v>107</v>
       </c>
@@ -1689,7 +1689,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" s="5">
         <v>108</v>
       </c>
@@ -1721,7 +1721,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:6">
       <c r="A34" s="5">
         <v>110</v>
       </c>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:6">
       <c r="A35" s="5">
         <v>111</v>
       </c>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:6">
       <c r="A36" s="5">
         <v>112</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:6">
       <c r="A37" s="5">
         <v>113</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:6">
       <c r="A38" s="5">
         <v>114</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:6">
       <c r="A39" s="5">
         <v>115</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:6">
       <c r="A40" s="5">
         <v>116</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:6">
       <c r="A41" s="5">
         <v>117</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:6">
       <c r="A42" s="5">
         <v>118</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:6">
       <c r="A43" s="5">
         <v>119</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:6">
       <c r="A44" s="5">
         <v>120</v>
       </c>

--- a/hall/resources/sample/GrowthFund.xlsx
+++ b/hall/resources/sample/GrowthFund.xlsx
@@ -91,88 +91,88 @@
     <t>getItem</t>
   </si>
   <si>
-    <t>1990000_66000</t>
-  </si>
-  <si>
-    <t>1990000_131000</t>
-  </si>
-  <si>
-    <t>1990000_202000</t>
-  </si>
-  <si>
-    <t>1990000_273000</t>
-  </si>
-  <si>
-    <t>1990000_294000</t>
-  </si>
-  <si>
-    <t>1990000_402000</t>
-  </si>
-  <si>
-    <t>1990000_510000</t>
-  </si>
-  <si>
-    <t>1990000_628000</t>
-  </si>
-  <si>
-    <t>1990000_764000</t>
-  </si>
-  <si>
-    <t>1990000_774000</t>
-  </si>
-  <si>
-    <t>1990000_1002000</t>
-  </si>
-  <si>
-    <t>1990000_1230000</t>
-  </si>
-  <si>
-    <t>1990000_1371000</t>
-  </si>
-  <si>
-    <t>1990000_1695000</t>
-  </si>
-  <si>
-    <t>1990000_350000</t>
-  </si>
-  <si>
-    <t>1990000_694000</t>
-  </si>
-  <si>
-    <t>1990000_1071000</t>
-  </si>
-  <si>
-    <t>1990000_1447000</t>
-  </si>
-  <si>
-    <t>1990000_1555000</t>
-  </si>
-  <si>
-    <t>1990000_2128000</t>
-  </si>
-  <si>
-    <t>1990000_2701000</t>
-  </si>
-  <si>
-    <t>1990000_3326000</t>
-  </si>
-  <si>
-    <t>1990000_4042000</t>
-  </si>
-  <si>
-    <t>1990000_4095000</t>
-  </si>
-  <si>
-    <t>1990000_5302000</t>
-  </si>
-  <si>
-    <t>1990000_6509000</t>
-  </si>
-  <si>
-    <t>1990000_7255000</t>
-  </si>
-  <si>
-    <t>1990000_8969000</t>
+    <t>1990000_26000</t>
+  </si>
+  <si>
+    <t>1990000_52000</t>
+  </si>
+  <si>
+    <t>1990000_81000</t>
+  </si>
+  <si>
+    <t>1990000_109000</t>
+  </si>
+  <si>
+    <t>1990000_118000</t>
+  </si>
+  <si>
+    <t>1990000_161000</t>
+  </si>
+  <si>
+    <t>1990000_204000</t>
+  </si>
+  <si>
+    <t>1990000_251000</t>
+  </si>
+  <si>
+    <t>1990000_305000</t>
+  </si>
+  <si>
+    <t>1990000_310000</t>
+  </si>
+  <si>
+    <t>1990000_401000</t>
+  </si>
+  <si>
+    <t>1990000_492000</t>
+  </si>
+  <si>
+    <t>1990000_548000</t>
+  </si>
+  <si>
+    <t>1990000_678000</t>
+  </si>
+  <si>
+    <t>1990000_80000</t>
+  </si>
+  <si>
+    <t>1990000_159000</t>
+  </si>
+  <si>
+    <t>1990000_245000</t>
+  </si>
+  <si>
+    <t>1990000_331000</t>
+  </si>
+  <si>
+    <t>1990000_356000</t>
+  </si>
+  <si>
+    <t>1990000_486000</t>
+  </si>
+  <si>
+    <t>1990000_617000</t>
+  </si>
+  <si>
+    <t>1990000_760000</t>
+  </si>
+  <si>
+    <t>1990000_924000</t>
+  </si>
+  <si>
+    <t>1990000_936000</t>
+  </si>
+  <si>
+    <t>1990000_1212000</t>
+  </si>
+  <si>
+    <t>1990000_1488000</t>
+  </si>
+  <si>
+    <t>1990000_1658000</t>
+  </si>
+  <si>
+    <t>1990000_2050000</t>
   </si>
 </sst>
 </file>

--- a/hall/resources/sample/GrowthFund.xlsx
+++ b/hall/resources/sample/GrowthFund.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="GrowthFund" sheetId="1" r:id="rId1"/>
@@ -91,88 +91,88 @@
     <t>getItem</t>
   </si>
   <si>
-    <t>1990000_26000</t>
-  </si>
-  <si>
-    <t>1990000_52000</t>
+    <t>1990000_2100</t>
+  </si>
+  <si>
+    <t>1990000_4300</t>
+  </si>
+  <si>
+    <t>1990000_6600</t>
+  </si>
+  <si>
+    <t>1990000_8900</t>
+  </si>
+  <si>
+    <t>1990000_9500</t>
+  </si>
+  <si>
+    <t>1990000_13100</t>
+  </si>
+  <si>
+    <t>1990000_16600</t>
+  </si>
+  <si>
+    <t>1990000_20400</t>
+  </si>
+  <si>
+    <t>1990000_24800</t>
+  </si>
+  <si>
+    <t>1990000_25100</t>
+  </si>
+  <si>
+    <t>1990000_32500</t>
+  </si>
+  <si>
+    <t>1990000_39900</t>
+  </si>
+  <si>
+    <t>1990000_44500</t>
+  </si>
+  <si>
+    <t>1990000_55000</t>
+  </si>
+  <si>
+    <t>1990000_20000</t>
+  </si>
+  <si>
+    <t>1990000_39000</t>
+  </si>
+  <si>
+    <t>1990000_60000</t>
   </si>
   <si>
     <t>1990000_81000</t>
   </si>
   <si>
-    <t>1990000_109000</t>
-  </si>
-  <si>
-    <t>1990000_118000</t>
-  </si>
-  <si>
-    <t>1990000_161000</t>
-  </si>
-  <si>
-    <t>1990000_204000</t>
-  </si>
-  <si>
-    <t>1990000_251000</t>
-  </si>
-  <si>
-    <t>1990000_305000</t>
-  </si>
-  <si>
-    <t>1990000_310000</t>
-  </si>
-  <si>
-    <t>1990000_401000</t>
-  </si>
-  <si>
-    <t>1990000_492000</t>
-  </si>
-  <si>
-    <t>1990000_548000</t>
-  </si>
-  <si>
-    <t>1990000_678000</t>
-  </si>
-  <si>
-    <t>1990000_80000</t>
-  </si>
-  <si>
-    <t>1990000_159000</t>
-  </si>
-  <si>
-    <t>1990000_245000</t>
-  </si>
-  <si>
-    <t>1990000_331000</t>
-  </si>
-  <si>
-    <t>1990000_356000</t>
-  </si>
-  <si>
-    <t>1990000_486000</t>
-  </si>
-  <si>
-    <t>1990000_617000</t>
-  </si>
-  <si>
-    <t>1990000_760000</t>
-  </si>
-  <si>
-    <t>1990000_924000</t>
-  </si>
-  <si>
-    <t>1990000_936000</t>
-  </si>
-  <si>
-    <t>1990000_1212000</t>
-  </si>
-  <si>
-    <t>1990000_1488000</t>
-  </si>
-  <si>
-    <t>1990000_1658000</t>
-  </si>
-  <si>
-    <t>1990000_2050000</t>
+    <t>1990000_87000</t>
+  </si>
+  <si>
+    <t>1990000_120000</t>
+  </si>
+  <si>
+    <t>1990000_152000</t>
+  </si>
+  <si>
+    <t>1990000_187000</t>
+  </si>
+  <si>
+    <t>1990000_227000</t>
+  </si>
+  <si>
+    <t>1990000_230000</t>
+  </si>
+  <si>
+    <t>1990000_298000</t>
+  </si>
+  <si>
+    <t>1990000_366000</t>
+  </si>
+  <si>
+    <t>1990000_408000</t>
+  </si>
+  <si>
+    <t>1990000_504000</t>
   </si>
 </sst>
 </file>

--- a/hall/resources/sample/GrowthFund.xlsx
+++ b/hall/resources/sample/GrowthFund.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GrowthFund" sheetId="1" r:id="rId1"/>
@@ -91,88 +91,88 @@
     <t>getItem</t>
   </si>
   <si>
-    <t>1990000_2100</t>
-  </si>
-  <si>
-    <t>1990000_4300</t>
-  </si>
-  <si>
-    <t>1990000_6600</t>
-  </si>
-  <si>
-    <t>1990000_8900</t>
-  </si>
-  <si>
-    <t>1990000_9500</t>
-  </si>
-  <si>
-    <t>1990000_13100</t>
-  </si>
-  <si>
-    <t>1990000_16600</t>
-  </si>
-  <si>
-    <t>1990000_20400</t>
-  </si>
-  <si>
-    <t>1990000_24800</t>
-  </si>
-  <si>
-    <t>1990000_25100</t>
-  </si>
-  <si>
-    <t>1990000_32500</t>
-  </si>
-  <si>
-    <t>1990000_39900</t>
-  </si>
-  <si>
-    <t>1990000_44500</t>
-  </si>
-  <si>
-    <t>1990000_55000</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>1990000_39000</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
+    <t>1990000_26000</t>
+  </si>
+  <si>
+    <t>1990000_52000</t>
   </si>
   <si>
     <t>1990000_81000</t>
   </si>
   <si>
-    <t>1990000_87000</t>
-  </si>
-  <si>
-    <t>1990000_120000</t>
-  </si>
-  <si>
-    <t>1990000_152000</t>
-  </si>
-  <si>
-    <t>1990000_187000</t>
-  </si>
-  <si>
-    <t>1990000_227000</t>
-  </si>
-  <si>
-    <t>1990000_230000</t>
-  </si>
-  <si>
-    <t>1990000_298000</t>
-  </si>
-  <si>
-    <t>1990000_366000</t>
-  </si>
-  <si>
-    <t>1990000_408000</t>
-  </si>
-  <si>
-    <t>1990000_504000</t>
+    <t>1990000_109000</t>
+  </si>
+  <si>
+    <t>1990000_118000</t>
+  </si>
+  <si>
+    <t>1990000_161000</t>
+  </si>
+  <si>
+    <t>1990000_204000</t>
+  </si>
+  <si>
+    <t>1990000_251000</t>
+  </si>
+  <si>
+    <t>1990000_305000</t>
+  </si>
+  <si>
+    <t>1990000_310000</t>
+  </si>
+  <si>
+    <t>1990000_401000</t>
+  </si>
+  <si>
+    <t>1990000_492000</t>
+  </si>
+  <si>
+    <t>1990000_548000</t>
+  </si>
+  <si>
+    <t>1990000_678000</t>
+  </si>
+  <si>
+    <t>1990000_80000</t>
+  </si>
+  <si>
+    <t>1990000_159000</t>
+  </si>
+  <si>
+    <t>1990000_245000</t>
+  </si>
+  <si>
+    <t>1990000_331000</t>
+  </si>
+  <si>
+    <t>1990000_356000</t>
+  </si>
+  <si>
+    <t>1990000_486000</t>
+  </si>
+  <si>
+    <t>1990000_617000</t>
+  </si>
+  <si>
+    <t>1990000_760000</t>
+  </si>
+  <si>
+    <t>1990000_924000</t>
+  </si>
+  <si>
+    <t>1990000_936000</t>
+  </si>
+  <si>
+    <t>1990000_1212000</t>
+  </si>
+  <si>
+    <t>1990000_1488000</t>
+  </si>
+  <si>
+    <t>1990000_1658000</t>
+  </si>
+  <si>
+    <t>1990000_2050000</t>
   </si>
 </sst>
 </file>

--- a/hall/resources/sample/GrowthFund.xlsx
+++ b/hall/resources/sample/GrowthFund.xlsx
@@ -91,88 +91,88 @@
     <t>getItem</t>
   </si>
   <si>
-    <t>1990000_2100</t>
-  </si>
-  <si>
-    <t>1990000_4300</t>
-  </si>
-  <si>
-    <t>1990000_6600</t>
-  </si>
-  <si>
-    <t>1990000_8900</t>
-  </si>
-  <si>
-    <t>1990000_9500</t>
-  </si>
-  <si>
-    <t>1990000_13100</t>
-  </si>
-  <si>
-    <t>1990000_16600</t>
-  </si>
-  <si>
-    <t>1990000_20400</t>
-  </si>
-  <si>
-    <t>1990000_24800</t>
-  </si>
-  <si>
-    <t>1990000_25100</t>
-  </si>
-  <si>
-    <t>1990000_32500</t>
-  </si>
-  <si>
-    <t>1990000_39900</t>
-  </si>
-  <si>
-    <t>1990000_44500</t>
-  </si>
-  <si>
-    <t>1990000_55000</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>1990000_39000</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
-  </si>
-  <si>
-    <t>1990000_81000</t>
-  </si>
-  <si>
-    <t>1990000_87000</t>
-  </si>
-  <si>
-    <t>1990000_120000</t>
-  </si>
-  <si>
-    <t>1990000_152000</t>
-  </si>
-  <si>
-    <t>1990000_187000</t>
-  </si>
-  <si>
-    <t>1990000_227000</t>
-  </si>
-  <si>
-    <t>1990000_230000</t>
-  </si>
-  <si>
-    <t>1990000_298000</t>
-  </si>
-  <si>
-    <t>1990000_366000</t>
-  </si>
-  <si>
-    <t>1990000_408000</t>
-  </si>
-  <si>
-    <t>1990000_504000</t>
+    <t>1990000_17900</t>
+  </si>
+  <si>
+    <t>1990000_35500</t>
+  </si>
+  <si>
+    <t>1990000_54700</t>
+  </si>
+  <si>
+    <t>1990000_74000</t>
+  </si>
+  <si>
+    <t>1990000_79500</t>
+  </si>
+  <si>
+    <t>1990000_108800</t>
+  </si>
+  <si>
+    <t>1990000_138000</t>
+  </si>
+  <si>
+    <t>1990000_170000</t>
+  </si>
+  <si>
+    <t>1990000_206500</t>
+  </si>
+  <si>
+    <t>1990000_209300</t>
+  </si>
+  <si>
+    <t>1990000_270900</t>
+  </si>
+  <si>
+    <t>1990000_332600</t>
+  </si>
+  <si>
+    <t>1990000_370700</t>
+  </si>
+  <si>
+    <t>1990000_458300</t>
+  </si>
+  <si>
+    <t>1990000_177000</t>
+  </si>
+  <si>
+    <t>1990000_351000</t>
+  </si>
+  <si>
+    <t>1990000_541000</t>
+  </si>
+  <si>
+    <t>1990000_732000</t>
+  </si>
+  <si>
+    <t>1990000_786000</t>
+  </si>
+  <si>
+    <t>1990000_1076000</t>
+  </si>
+  <si>
+    <t>1990000_1365000</t>
+  </si>
+  <si>
+    <t>1990000_1681000</t>
+  </si>
+  <si>
+    <t>1990000_2043000</t>
+  </si>
+  <si>
+    <t>1990000_2070000</t>
+  </si>
+  <si>
+    <t>1990000_2680000</t>
+  </si>
+  <si>
+    <t>1990000_3290000</t>
+  </si>
+  <si>
+    <t>1990000_3667000</t>
+  </si>
+  <si>
+    <t>1990000_4534000</t>
   </si>
 </sst>
 </file>

--- a/hall/resources/sample/GrowthFund.xlsx
+++ b/hall/resources/sample/GrowthFund.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="GrowthFund" sheetId="1" r:id="rId1"/>
@@ -91,88 +91,88 @@
     <t>getItem</t>
   </si>
   <si>
-    <t>1990000_26000</t>
-  </si>
-  <si>
-    <t>1990000_52000</t>
-  </si>
-  <si>
-    <t>1990000_81000</t>
-  </si>
-  <si>
-    <t>1990000_109000</t>
-  </si>
-  <si>
-    <t>1990000_118000</t>
-  </si>
-  <si>
-    <t>1990000_161000</t>
-  </si>
-  <si>
-    <t>1990000_204000</t>
-  </si>
-  <si>
-    <t>1990000_251000</t>
-  </si>
-  <si>
-    <t>1990000_305000</t>
-  </si>
-  <si>
-    <t>1990000_310000</t>
-  </si>
-  <si>
-    <t>1990000_401000</t>
-  </si>
-  <si>
-    <t>1990000_492000</t>
-  </si>
-  <si>
-    <t>1990000_548000</t>
-  </si>
-  <si>
-    <t>1990000_678000</t>
-  </si>
-  <si>
-    <t>1990000_80000</t>
-  </si>
-  <si>
-    <t>1990000_159000</t>
-  </si>
-  <si>
-    <t>1990000_245000</t>
-  </si>
-  <si>
-    <t>1990000_331000</t>
-  </si>
-  <si>
-    <t>1990000_356000</t>
-  </si>
-  <si>
-    <t>1990000_486000</t>
-  </si>
-  <si>
-    <t>1990000_617000</t>
-  </si>
-  <si>
-    <t>1990000_760000</t>
-  </si>
-  <si>
-    <t>1990000_924000</t>
-  </si>
-  <si>
-    <t>1990000_936000</t>
-  </si>
-  <si>
-    <t>1990000_1212000</t>
-  </si>
-  <si>
-    <t>1990000_1488000</t>
-  </si>
-  <si>
-    <t>1990000_1658000</t>
-  </si>
-  <si>
-    <t>1990000_2050000</t>
+    <t>1990000_17900</t>
+  </si>
+  <si>
+    <t>1990000_35500</t>
+  </si>
+  <si>
+    <t>1990000_54700</t>
+  </si>
+  <si>
+    <t>1990000_74000</t>
+  </si>
+  <si>
+    <t>1990000_79500</t>
+  </si>
+  <si>
+    <t>1990000_108800</t>
+  </si>
+  <si>
+    <t>1990000_138000</t>
+  </si>
+  <si>
+    <t>1990000_170000</t>
+  </si>
+  <si>
+    <t>1990000_206500</t>
+  </si>
+  <si>
+    <t>1990000_209300</t>
+  </si>
+  <si>
+    <t>1990000_270900</t>
+  </si>
+  <si>
+    <t>1990000_332600</t>
+  </si>
+  <si>
+    <t>1990000_370700</t>
+  </si>
+  <si>
+    <t>1990000_458300</t>
+  </si>
+  <si>
+    <t>1990000_177000</t>
+  </si>
+  <si>
+    <t>1990000_351000</t>
+  </si>
+  <si>
+    <t>1990000_541000</t>
+  </si>
+  <si>
+    <t>1990000_732000</t>
+  </si>
+  <si>
+    <t>1990000_786000</t>
+  </si>
+  <si>
+    <t>1990000_1076000</t>
+  </si>
+  <si>
+    <t>1990000_1365000</t>
+  </si>
+  <si>
+    <t>1990000_1681000</t>
+  </si>
+  <si>
+    <t>1990000_2043000</t>
+  </si>
+  <si>
+    <t>1990000_2070000</t>
+  </si>
+  <si>
+    <t>1990000_2680000</t>
+  </si>
+  <si>
+    <t>1990000_3290000</t>
+  </si>
+  <si>
+    <t>1990000_3667000</t>
+  </si>
+  <si>
+    <t>1990000_4534000</t>
   </si>
 </sst>
 </file>
